--- a/initial-setup.xlsx
+++ b/initial-setup.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\owenw\Documents\git\IBRAM\IBRAM-PATH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CA99592-825A-4BF0-9F6C-E1EA24A51A44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38DAAB02-6614-4B54-9CC5-89E83957D1B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9290" yWindow="1710" windowWidth="15840" windowHeight="18840" xr2:uid="{347F8A05-7FE6-41D9-B234-F6E3A31F4450}"/>
+    <workbookView xWindow="5450" yWindow="510" windowWidth="24570" windowHeight="19760" activeTab="5" xr2:uid="{347F8A05-7FE6-41D9-B234-F6E3A31F4450}"/>
   </bookViews>
   <sheets>
     <sheet name="project" sheetId="1" r:id="rId1"/>
     <sheet name="scenario" sheetId="2" r:id="rId2"/>
-    <sheet name="item" sheetId="3" r:id="rId3"/>
+    <sheet name="pathway" sheetId="3" r:id="rId3"/>
     <sheet name="pathwayPoint" sheetId="4" r:id="rId4"/>
     <sheet name="climateMap" sheetId="5" r:id="rId5"/>
     <sheet name="landCover" sheetId="6" r:id="rId6"/>
@@ -61,9 +61,6 @@
     <t>complete</t>
   </si>
   <si>
-    <t>item</t>
-  </si>
-  <si>
     <t>Used vehicles</t>
   </si>
   <si>
@@ -97,9 +94,6 @@
     <t>Fruit</t>
   </si>
   <si>
-    <t>itemId</t>
-  </si>
-  <si>
     <t>tableName</t>
   </si>
   <si>
@@ -428,6 +422,12 @@
   </si>
   <si>
     <t>OTHER_INDIGENOUS_VEGETATION</t>
+  </si>
+  <si>
+    <t>pathway</t>
+  </si>
+  <si>
+    <t>pathwayId</t>
   </si>
 </sst>
 </file>
@@ -829,13 +829,13 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D1" t="s">
+        <v>83</v>
+      </c>
+      <c r="E1" t="s">
         <v>84</v>
-      </c>
-      <c r="D1" t="s">
-        <v>85</v>
-      </c>
-      <c r="E1" t="s">
-        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -867,10 +867,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D1" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="E1" t="s">
         <v>2</v>
@@ -882,7 +882,7 @@
         <v>4</v>
       </c>
       <c r="H1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="I1" t="s">
         <v>5</v>
@@ -912,7 +912,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -920,7 +920,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -928,7 +928,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -936,7 +936,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -944,7 +944,7 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -952,7 +952,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -960,7 +960,7 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -968,7 +968,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -976,7 +976,7 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -984,7 +984,7 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -992,7 +992,7 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -1004,6 +1004,15 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEAC2F6F-791C-4FEA-BDCF-DA9E2756138C}">
   <dimension ref="A1:G31"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="2.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.08984375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.90625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="7" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.26953125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
@@ -1013,19 +1022,19 @@
         <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>6</v>
+        <v>127</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>128</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>19</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.35">
@@ -1033,22 +1042,22 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D2" s="1">
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>23</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.35">
@@ -1056,22 +1065,22 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.35">
@@ -1079,22 +1088,22 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D4" s="1">
         <v>1</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.35">
@@ -1102,19 +1111,19 @@
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D5" s="1">
         <v>1</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G5" s="1">
         <v>1000000</v>
@@ -1125,22 +1134,22 @@
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.35">
@@ -1148,22 +1157,22 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D7" s="1">
         <v>2</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.35">
@@ -1171,22 +1180,22 @@
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D8" s="1">
         <v>2</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
@@ -1194,22 +1203,22 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D9" s="1">
         <v>3</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
@@ -1217,22 +1226,22 @@
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D10" s="1">
         <v>4</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
@@ -1240,19 +1249,19 @@
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D11" s="1">
         <v>4</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G11" s="1">
         <v>1000000</v>
@@ -1263,22 +1272,22 @@
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D12" s="1">
         <v>5</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
@@ -1286,22 +1295,22 @@
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D13" s="1">
         <v>5</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.35">
@@ -1309,22 +1318,22 @@
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D14" s="1">
         <v>5</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.35">
@@ -1332,19 +1341,19 @@
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D15" s="1">
         <v>5</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G15" s="1">
         <v>1000000</v>
@@ -1355,22 +1364,22 @@
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D16" s="1">
         <v>6</v>
       </c>
       <c r="E16" s="1" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
@@ -1378,19 +1387,19 @@
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D17" s="1">
         <v>6</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G17" s="1">
         <v>1000000</v>
@@ -1401,22 +1410,22 @@
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D18" s="1">
         <v>7</v>
       </c>
       <c r="E18" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
@@ -1424,19 +1433,19 @@
         <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D19" s="1">
         <v>7</v>
       </c>
       <c r="E19" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G19" s="1">
         <v>1000000</v>
@@ -1447,22 +1456,22 @@
         <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D20" s="1">
         <v>8</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
@@ -1470,22 +1479,22 @@
         <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D21" s="1">
         <v>8</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.35">
@@ -1493,19 +1502,19 @@
         <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D22" s="1">
         <v>8</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G22" s="1">
         <v>1000000</v>
@@ -1516,19 +1525,19 @@
         <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D23" s="1">
         <v>9</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G23" s="1">
         <v>1000000</v>
@@ -1539,22 +1548,22 @@
         <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D24" s="1">
         <v>10</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.35">
@@ -1562,22 +1571,22 @@
         <v>24</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D25" s="1">
         <v>10</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.35">
@@ -1585,22 +1594,22 @@
         <v>25</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D26" s="1">
         <v>10</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.35">
@@ -1608,19 +1617,19 @@
         <v>26</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D27" s="1">
         <v>10</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G27" s="1">
         <v>1000000</v>
@@ -1631,22 +1640,22 @@
         <v>27</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D28" s="1">
         <v>11</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.35">
@@ -1654,22 +1663,22 @@
         <v>28</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D29" s="1">
         <v>11</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.35">
@@ -1677,22 +1686,22 @@
         <v>29</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D30" s="1">
         <v>11</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.35">
@@ -1700,19 +1709,19 @@
         <v>30</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="D31" s="1">
         <v>11</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G31" s="1">
         <v>1000000</v>
@@ -1739,7 +1748,7 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.35">
@@ -1747,10 +1756,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C2" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.35">
@@ -1758,10 +1767,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.35">
@@ -1769,10 +1778,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C4" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.35">
@@ -1780,10 +1789,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.35">
@@ -1791,10 +1800,10 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C6" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.35">
@@ -1802,10 +1811,10 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.35">
@@ -1813,10 +1822,10 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.35">
@@ -1824,10 +1833,10 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="C9" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="10" spans="1:3" x14ac:dyDescent="0.35">
@@ -1835,10 +1844,10 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C10" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="11" spans="1:3" x14ac:dyDescent="0.35">
@@ -1846,10 +1855,10 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C11" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="1:3" x14ac:dyDescent="0.35">
@@ -1857,10 +1866,10 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C12" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.35">
@@ -1868,10 +1877,10 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C13" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="14" spans="1:3" x14ac:dyDescent="0.35">
@@ -1879,10 +1888,10 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C14" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:3" x14ac:dyDescent="0.35">
@@ -1890,10 +1899,10 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C15" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="16" spans="1:3" x14ac:dyDescent="0.35">
@@ -1901,10 +1910,10 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C16" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17" spans="1:3" x14ac:dyDescent="0.35">
@@ -1912,10 +1921,10 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C17" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="18" spans="1:3" x14ac:dyDescent="0.35">
@@ -1923,10 +1932,10 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="C18" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="19" spans="1:3" x14ac:dyDescent="0.35">
@@ -1934,10 +1943,10 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="C19" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
     </row>
     <row r="20" spans="1:3" x14ac:dyDescent="0.35">
@@ -1945,10 +1954,10 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="C20" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
     </row>
     <row r="21" spans="1:3" x14ac:dyDescent="0.35">
@@ -1956,10 +1965,10 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C21" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:3" x14ac:dyDescent="0.35">
@@ -1967,10 +1976,10 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C22" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="23" spans="1:3" x14ac:dyDescent="0.35">
@@ -1978,10 +1987,10 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="C23" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:3" x14ac:dyDescent="0.35">
@@ -1989,10 +1998,10 @@
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="C24" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
     </row>
     <row r="25" spans="1:3" x14ac:dyDescent="0.35">
@@ -2000,10 +2009,10 @@
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C25" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:3" x14ac:dyDescent="0.35">
@@ -2011,10 +2020,10 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C26" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="27" spans="1:3" x14ac:dyDescent="0.35">
@@ -2022,10 +2031,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C27" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
     </row>
     <row r="28" spans="1:3" x14ac:dyDescent="0.35">
@@ -2033,10 +2042,10 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:3" x14ac:dyDescent="0.35">
@@ -2044,10 +2053,10 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C29" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -2073,7 +2082,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
@@ -2081,7 +2090,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
@@ -2089,7 +2098,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
@@ -2097,7 +2106,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
@@ -2105,7 +2114,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
@@ -2113,7 +2122,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
@@ -2121,7 +2130,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
@@ -2129,7 +2138,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.35">
@@ -2137,7 +2146,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.35">
@@ -2145,7 +2154,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.35">
@@ -2153,7 +2162,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.35">
@@ -2161,7 +2170,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.35">
@@ -2169,7 +2178,7 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>
